--- a/docs/downloads/04/tbl_class_marovoay_madiromiongana.xlsx
+++ b/docs/downloads/04/tbl_class_marovoay_madiromiongana.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -397,12 +397,6 @@
           <t>Inconnu</t>
         </is>
       </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>2.9</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -555,14 +549,8 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D9">
-        <v>4</v>
-      </c>
-      <c r="E9">
-        <v>7.1</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -578,14 +566,8 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Inconnu</t>
-        </is>
-      </c>
-      <c r="D10">
-        <v>2</v>
-      </c>
-      <c r="E10">
-        <v>33.3</v>
+          <t>Primaire</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -601,14 +583,8 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Primaire</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>4</v>
-      </c>
-      <c r="E11">
-        <v>66.7</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -624,14 +600,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D12">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="E12">
-        <v>18.6</v>
+        <v>81.40000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -647,14 +623,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D13">
-        <v>35</v>
+        <v>8</v>
       </c>
       <c r="E13">
-        <v>81.40000000000001</v>
+        <v>18.6</v>
       </c>
     </row>
     <row r="14">
@@ -673,12 +649,6 @@
           <t>Inconnu</t>
         </is>
       </c>
-      <c r="D14">
-        <v>4</v>
-      </c>
-      <c r="E14">
-        <v>1.8</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -739,14 +709,8 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
-        </is>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17">
-        <v>0.5</v>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
       </c>
     </row>
     <row r="18">
@@ -808,7 +772,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D20">
@@ -877,14 +841,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Secondaire 2ème cycle</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D23">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="E23">
-        <v>12</v>
+        <v>15.1</v>
       </c>
     </row>
     <row r="24">
@@ -895,19 +859,13 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18-25 ans</t>
+          <t>3-5 ans</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Universitaire</t>
-        </is>
-      </c>
-      <c r="D24">
-        <v>9</v>
-      </c>
-      <c r="E24">
-        <v>3.2</v>
+          <t>Inconnu</t>
+        </is>
       </c>
     </row>
     <row r="25">
@@ -923,14 +881,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Inconnu</t>
+          <t>Primaire</t>
         </is>
       </c>
       <c r="D25">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E25">
-        <v>55.6</v>
+        <v>44.4</v>
       </c>
     </row>
     <row r="26">
@@ -946,14 +904,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Primaire</t>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
         </is>
       </c>
       <c r="D26">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E26">
-        <v>44.4</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="27">
@@ -972,12 +930,6 @@
           <t>Inconnu</t>
         </is>
       </c>
-      <c r="D27">
-        <v>39</v>
-      </c>
-      <c r="E27">
-        <v>14.1</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1018,11 +970,28 @@
           <t>Secondaire 1er cycle</t>
         </is>
       </c>
-      <c r="D29">
-        <v>2</v>
-      </c>
-      <c r="E29">
-        <v>0.7</v>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Marovoay - Tous</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>6-10 ans</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Secondaire 2ème cycle &amp; sup.</t>
+        </is>
+      </c>
+      <c r="D30">
+        <v>35</v>
+      </c>
+      <c r="E30">
+        <v>12.6</v>
       </c>
     </row>
   </sheetData>
